--- a/STAGING/claude-folio-assistant-core-migration-w5wmag/ihris5/publisher/StructureDefinition-iHRISReportElement.xlsx
+++ b/STAGING/claude-folio-assistant-core-migration-w5wmag/ihris5/publisher/StructureDefinition-iHRISReportElement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T11:48:54+00:00</t>
+    <t>2026-10-09T11:54:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
